--- a/output/arxiv_3d_anomaly_detection_202601-202610.xlsx
+++ b/output/arxiv_3d_anomaly_detection_202601-202610.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,6 +31,14 @@
     <font>
       <color rgb="000563C1"/>
       <u val="single"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFED7D31"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF2E7D32"/>
     </font>
   </fonts>
   <fills count="2">
@@ -53,7 +61,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -62,6 +70,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -435,6 +449,7 @@
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -463,6 +478,11 @@
           <t>分类</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -490,6 +510,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>5 pages, 3 figures, Under Review</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -517,6 +542,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Accepted by NeurIPS 2026. Code: https://github.com/VisualScienceLab-KHU/GRIM</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -544,6 +574,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -571,6 +602,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -598,6 +630,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17 pages, including 6 pages of supplementary material. Code: https://github.com/gyutong406-commits/PC2-AD</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -625,6 +662,7 @@
           <t>cs.DC</t>
         </is>
       </c>
+      <c r="F7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -652,6 +690,7 @@
           <t>physics.ins-det</t>
         </is>
       </c>
+      <c r="F8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -679,6 +718,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -706,6 +746,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -733,6 +774,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Summary of the 10th AI City Challenge Workshop in conjunction with ECCV 2026</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -760,6 +806,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -787,6 +834,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -814,6 +862,11 @@
           <t>cs.GR</t>
         </is>
       </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>ICIG 2026 oral presentation, 13 pages, 3 tables, 4 figures</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -841,6 +894,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -868,6 +922,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -895,6 +950,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -922,6 +978,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Accepted to ECCV 2026 (oral)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -949,6 +1010,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -976,6 +1038,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1003,6 +1066,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1030,6 +1094,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>16 pages, 6 figures</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1057,6 +1126,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>accepted by ACM MM 2026</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1084,6 +1158,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>20 pages; already accepted by Pattern Recognition</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1111,6 +1190,11 @@
           <t>cond-mat.str-el</t>
         </is>
       </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1138,6 +1222,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1165,6 +1250,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1192,6 +1278,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1219,6 +1306,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>ICML 2026</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1246,6 +1338,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Accepted by ECCV2026</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1273,6 +1370,11 @@
           <t>cs.RO</t>
         </is>
       </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>The Aerial Inspection for Marine Infrastructures (AIMI) workshop</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1300,6 +1402,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Accepted to ECCV 2026! Project page: https://cmds-ad.github.io/</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1327,6 +1434,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1354,6 +1462,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1381,6 +1490,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1408,6 +1518,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1435,6 +1546,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>This work has been submitted IEEE for potential publication</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1462,6 +1578,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1489,6 +1606,7 @@
           <t>cs.LG</t>
         </is>
       </c>
+      <c r="F39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1516,6 +1634,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Accepted to CVPR 2025. 15 pages</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1543,6 +1666,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1570,6 +1694,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Accepted to CVPR 2026, at the 9th Workshop on Efficient Deep Learning for Computer Vision (ECV). To be published in the IEEE/CVF CVPR 2026 Workshop Proceedings</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1597,6 +1726,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1624,6 +1754,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1651,6 +1782,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1678,6 +1810,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>12 pages</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1705,6 +1842,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1732,6 +1870,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1759,6 +1898,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>10 pages, 5 figures, 6 tables</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1786,6 +1930,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>Accepted at CVPR Findings 2026</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1813,6 +1962,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Resources: https://github.com/hzzzzzhappy/open-industry</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1840,6 +1994,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>Accepted to CVPR 2026. The source code is publicly available at https://github.com/7uHeng/ProOOD</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1867,6 +2026,11 @@
           <t>cond-mat.mtrl-sci</t>
         </is>
       </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>main text 18 pages, 4 figures</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1894,6 +2058,7 @@
           <t>stat.ME</t>
         </is>
       </c>
+      <c r="F54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1921,6 +2086,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Accepted by CVPR 2026</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1948,6 +2118,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>Accepted at ECCV26. Project Page: https://chumsy0725.github.io/3DGS-Uncertainty/</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1975,6 +2150,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Accepted for publication in IEEE Transactions on Circuits and Systems for Video Technology (TCSVT)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2002,6 +2182,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2029,6 +2214,11 @@
           <t>cs.RO</t>
         </is>
       </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Under review</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2056,6 +2246,7 @@
           <t>cs.RO</t>
         </is>
       </c>
+      <c r="F60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2083,6 +2274,11 @@
           <t>physics.plasm-ph</t>
         </is>
       </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Substantial Revision Required</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2110,6 +2306,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2137,6 +2334,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2164,6 +2362,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>draft paper</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2191,6 +2394,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Accepted by CVPR 2026</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2218,6 +2426,11 @@
           <t>eess.SP</t>
         </is>
       </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>International Journal of Engineering Research and Innovation | v17, n2, Fall/Winter 2025</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2245,6 +2458,11 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Accepted for MIDL 2026</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2272,6 +2490,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2299,6 +2518,7 @@
           <t>eess.IV</t>
         </is>
       </c>
+      <c r="F69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2326,6 +2546,11 @@
           <t>cond-mat.quant-gas</t>
         </is>
       </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>14 pages, 5 figures, to appear in PRA</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2353,6 +2578,11 @@
           <t>cs.LG</t>
         </is>
       </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>ICML 2026, camera-ready version, 24 pages</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2380,6 +2610,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2407,6 +2638,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2434,6 +2666,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2461,6 +2694,11 @@
           <t>astro-ph.GA</t>
         </is>
       </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>41 pages (main part) + 39 pages (appendix), revised version for the AAS journals</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2488,6 +2726,7 @@
           <t>cs.CV</t>
         </is>
       </c>
+      <c r="F76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2515,6 +2754,11 @@
           <t>stat.AP</t>
         </is>
       </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>28 pages, 12 figures</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2542,6 +2786,7 @@
           <t>cs.LG</t>
         </is>
       </c>
+      <c r="F78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2567,6 +2812,11 @@
       <c r="E79" t="inlineStr">
         <is>
           <t>cs.CV</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>8 pages, 2 figures. This paper has been accepted at Bildverarbeitung für die Medizin (BVM) 2026</t>
         </is>
       </c>
     </row>
